--- a/Check.xlsx
+++ b/Check.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="1" r:id="R99fe3872b73f47ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="1" r:id="Rd9c1ddcadac2487a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,12 +50,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ui/AuthFragment.kt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Не выполнено</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Нет наблюдения на устройстве</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Планируется после принятия первой части</x:t>
@@ -1350,7 +1344,7 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="43.5">
+    <x:row r="2" ht="60" customHeight="1">
       <x:c r="A2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
@@ -1363,1551 +1357,1754 @@
       <x:c r="D2" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E2" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="str">
+        <x:v>Вход login2 выполнен. Открыта главная с меню и тремя новостями. HTTP login и userInfo: 200.</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>evidence/TC001-main.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="76" customHeight="1">
+      <x:c r="A3" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="B3" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="43.5">
-      <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E3" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>При пустых полях отображается сообщение о пустых логине и пароле; форма входа остаётся открыта.</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="43.5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>evidence/TC002-empty.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E4" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>Логин заполнен, пароль пуст. Отображается сообщение о пустых реквизитах; перехода нет.</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="43.5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>evidence/TC003-empty-password.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E5" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:v>Логин пуст, пароль заполнен. Отображается сообщение о пустых реквизитах; перехода нет.</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43.5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>evidence/TC004-empty-login.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E6" s="1" t="str">
+        <x:v>Не пройдено</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>Несуществующие реквизиты отклонены, но вместо Неверный логин или пароль показано Что-то пошло не так. Попробуйте позднее. HTTP401. Использован логин invalid-diploma-login.</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="43.5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>evidence/TC005-invalid-error.png
+evidence/auth-http-status.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="E7" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="str">
+        <x:v>В обоих полях по три пробела. Отображается сообщение о пустых реквизитах; вход не выполнен.</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="43.5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>evidence/TC006-spaces.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="156" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="str">
+        <x:v>Не пройдено</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:v>После выхода открыта форма входа. При последующем повороте приложение завершилось и появился домашний экран Android. В AndroidRuntime FATAL EXCEPTION: OkHttp Dispatcher; IllegalStateException: User must be authorized. После нового запуска доступна форма входа.</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>evidence/TC007-crash.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="76" customHeight="1">
+      <x:c r="A9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="43.5">
-      <x:c r="A9" s="1" t="s">
+      <x:c r="C9" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="E9" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="str">
+        <x:v>Главная сохранилась после поворота и возврата, пересоздавших Activity. Повторный вход не потребовался.</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>evidence/TC008-session-rotation.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="B10" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="43.5">
-      <x:c r="A10" s="1" t="s">
+      <x:c r="C10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="E10" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="str">
+        <x:v>Раздел миссии открыт, заголовок Главное - жить любя, список цитат непустой.</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H10" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>evidence/TC009-mission.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="60" customHeight="1">
+      <x:c r="A11" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="B11" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="43.5">
-      <x:c r="A11" s="1" t="s">
+      <x:c r="C11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="E11" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:v>Первая цитата раскрывает непустое пояснение. Повторное нажатие скрывает пояснение.</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H11" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>evidence/TC010-expanded.png
+evidence/TC010-collapsed.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="60" customHeight="1">
+      <x:c r="A12" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="B12" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="43.5">
-      <x:c r="A12" s="1" t="s">
+      <x:c r="C12" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="str">
+        <x:v>Пункт Главная в меню раздела миссии вернул на главную с блоком новостей.</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H12" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>evidence/TC011-home.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="76" customHeight="1">
+      <x:c r="A13" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="B13" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="43.5">
-      <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="str">
+        <x:v>Пункт Новости открыл список из шести новостей. Доступны сортировка, фильтр и панель управления.</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>evidence/TC012-news.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
+      <x:c r="A14" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="43.5">
-      <x:c r="A14" s="1" t="s">
+      <x:c r="C14" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="str">
+        <x:v>Из списка новостей пункт Главная открыл главную с тремя карточками и Все новости.</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>evidence/TC013-home.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="108" customHeight="1">
+      <x:c r="A15" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="B15" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="43.5">
-      <x:c r="A15" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="E15" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>Зафиксированы все шесть карточек. Первое нажатие полностью развернуло последовательность; второе восстановило исходный порядок. Даты 20 и 21 октября 2026.</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>evidence/TC014-before.xml
+evidence/TC014-reversed.xml
+evidence/TC014-restored.xml
+evidence/TC014-reversed.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="76" customHeight="1">
+      <x:c r="A16" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="B16" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="43.5">
-      <x:c r="A16" s="1" t="s">
+      <x:c r="C16" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="E16" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="str">
+        <x:v>Описание первой новости отображается после раскрытия и отсутствует в дереве UI после сворачивания.</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H16" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>evidence/TC015-expanded.png
+evidence/TC015-collapsed.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="76" customHeight="1">
+      <x:c r="A17" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="B17" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="43.5">
-      <x:c r="A17" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="E17" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="str">
+        <x:v>В фильтре публичных новостей есть категория, две даты и кнопки применения/отмены. Флаги статуса отсутствуют.</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H17" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>evidence/TC016-filter.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="B18" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="43.5">
-      <x:c r="A18" s="1" t="s">
+      <x:c r="C18" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="str">
+        <x:v>Отмена фильтра с обеими датами 23.10.2031 сохранила исходные шесть новостей.</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>evidence/TC017-future-filter.png
+evidence/TC017-cancelled.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
+      <x:c r="B19" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="43.5">
-      <x:c r="A19" s="1" t="s">
+      <x:c r="C19" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="str">
+        <x:v>Применён фильтр с пустыми полями. Сохранились все шесть исходных карточек и порядок дат.</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H19" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>evidence/TC018-empty-filter.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="60" customHeight="1">
+      <x:c r="A20" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="B20" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H19" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="43.5">
-      <x:c r="A20" s="1" t="s">
+      <x:c r="C20" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="str">
+        <x:v>Только начальная дата: показано Неверно указан период; после OK остаётся фильтр.</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H20" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>evidence/TC019-period-error.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="60" customHeight="1">
+      <x:c r="A21" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="B21" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="43.5">
-      <x:c r="A21" s="1" t="s">
+      <x:c r="C21" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="str">
+        <x:v>Только конечная дата: показано Неверно указан период; после OK остаётся фильтр.</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H21" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>evidence/TC020-period-error.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="60" customHeight="1">
+      <x:c r="A22" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
+      <x:c r="B22" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="43.5">
-      <x:c r="A22" s="1" t="s">
+      <x:c r="C22" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="str">
+        <x:v>В фильтре панели оба флага активности доступны и отмечены по умолчанию.</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H22" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>evidence/TC021-panel-filter.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="60" customHeight="1">
+      <x:c r="A23" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="B23" s="1" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="43.5">
-      <x:c r="A23" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="str">
+        <x:v>Форма создания содержит обязательные поля; переключатель Активна отмечен и недоступен.</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>evidence/TC022-create-form.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="60" customHeight="1">
+      <x:c r="A24" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="43.5">
-      <x:c r="A24" s="1" t="s">
+      <x:c r="C24" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="str">
+        <x:v>Пустая форма не сохранена; сообщение Заполните пустые поля и значки ошибок.</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H24" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>evidence/TC023-empty-form.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="76" customHeight="1">
+      <x:c r="A25" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="B25" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="43.5">
-      <x:c r="A25" s="1" t="s">
+      <x:c r="C25" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="str">
+        <x:v>Все поля кроме категории заполнены. Сохранение отклонено, значок у категории и сообщение Заполните пустые поля.</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H25" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>evidence/TC024-empty-category.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="76" customHeight="1">
+      <x:c r="A26" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
+      <x:c r="B26" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="43.5">
-      <x:c r="A26" s="1" t="s">
+      <x:c r="C26" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="str">
+        <x:v>Все поля кроме заголовка заполнены. Сохранение отклонено, значок у заголовка и сообщение Заполните пустые поля.</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H26" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>evidence/TC025-empty-title.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="92" customHeight="1">
+      <x:c r="A27" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
+      <x:c r="B27" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="43.5">
-      <x:c r="A27" s="1" t="s">
+      <x:c r="C27" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="str">
+        <x:v>Все поля кроме даты заполнены. Сохранение отклонено: значок у даты, сообщение Заполните пустые поля. Время 19:07 вместо образца 12:00.</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H27" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>evidence/TC026-empty-date.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="92" customHeight="1">
+      <x:c r="A28" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B27" s="1" t="s">
+      <x:c r="B28" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="43.5">
-      <x:c r="A28" s="1" t="s">
+      <x:c r="C28" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="str">
+        <x:v>Все поля кроме времени заполнены. Сохранение отклонено: значок у времени, сообщение Заполните пустые поля. Использована допустимая дата завтра.</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>evidence/TC027-empty-time.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="76" customHeight="1">
+      <x:c r="A29" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
+      <x:c r="B29" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="43.5">
-      <x:c r="A29" s="1" t="s">
+      <x:c r="C29" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="str">
+        <x:v>Все поля кроме описания заполнены. Сохранение отклонено, значок у описания и сообщение Заполните пустые поля.</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>evidence/TC028-empty-description.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="60" customHeight="1">
+      <x:c r="A30" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
+      <x:c r="B30" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="43.5">
-      <x:c r="A30" s="1" t="s">
+      <x:c r="C30" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="str">
+        <x:v>В пустой форме выбор Объявление автоматически заполнил заголовок Объявление.</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>evidence/TC029-announcement-autotitle.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
+      <x:c r="B31" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="43.5">
-      <x:c r="A31" s="1" t="s">
+      <x:c r="C31" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="str">
+        <x:v>При смене категории на Объявление пользовательский заголовок DIPLOMA-CUSTOM сохранён. Вместо образца Мой заголовок использована латиница.</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>evidence/TC030-custom-title.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="76" customHeight="1">
+      <x:c r="A32" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
+      <x:c r="B32" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H31" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="43.5">
-      <x:c r="A32" s="1" t="s">
+      <x:c r="C32" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="str">
+        <x:v>Подтверждение отмены заполненной формы вернуло в панель; DIPLOMA-CUSTOM в списке не появился.</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>evidence/TC032-cancel-dialog.png
+evidence/panel-baseline.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="92" customHeight="1">
+      <x:c r="A33" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
+      <x:c r="B33" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H32" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="43.5">
-      <x:c r="A33" s="1" t="s">
+      <x:c r="C33" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="str">
+        <x:v>Отмена выхода вернула заполненную форму с DIPLOMA-CUSTOM, датой, временем и описанием. Использовано другое уникальное имя черновика.</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>evidence/TC032-cancel-dialog.png
+evidence/TC032-preserved.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="92" customHeight="1">
+      <x:c r="A34" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="B34" s="1" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H33" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="43.5">
-      <x:c r="A34" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="str">
+        <x:v>Создана DIPLOMA-20261023-1905. После повторного открытия категория, заголовок, дата 23.10.2026, время 12:00 и описание совпали.</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>evidence/TC033-created.png
+evidence/TC033-reopened.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="76" customHeight="1">
+      <x:c r="A35" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
         <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="43.5">
-      <x:c r="A35" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B35" s="1" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="str">
+        <x:v>Заголовок и описание изменены с суффиксом -edited. Сохранены и подтверждены повторным открытием.</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>evidence/TC034-edited-reopened.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="76" customHeight="1">
+      <x:c r="A36" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" ht="29">
-      <x:c r="A36" s="1" t="s">
+      <x:c r="C36" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="str">
+        <x:v>Тестовая новость отключена; в панели НЕ АКТИВНА, при повторном открытии переключатель выключен.</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
+      <x:c r="I36" t="str">
+        <x:v>evidence/TC035-inactive-reopened.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="76" customHeight="1">
+      <x:c r="A37" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H36" s="1" t="s">
+      <x:c r="B37" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="29">
-      <x:c r="A37" s="1" t="s">
+      <x:c r="C37" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="str">
+        <x:v>Активность включена и сохранена. В панели АКТИВНА; повторное открытие подтвердило включённый переключатель.</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="I37" t="str">
+        <x:v>evidence/TC036-active-reopened.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="60" customHeight="1">
+      <x:c r="A38" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H37" s="1" t="s">
+      <x:c r="B38" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" ht="29">
-      <x:c r="A38" s="1" t="s">
+      <x:c r="C38" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
+      <x:c r="E38" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="str">
+        <x:v>Отмена подтверждения удаления оставила тестовую новость в панели.</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C38" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="I38" t="str">
+        <x:v>evidence/TC037-delete-dialog.png
+evidence/TC037-retained.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="92" customHeight="1">
+      <x:c r="A39" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H38" s="1" t="s">
+      <x:c r="B39" s="1" t="s">
         <x:v>105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="43.5">
-      <x:c r="A39" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="str">
+        <x:v>Подтверждено удаление собственной DIPLOMA-20261023-1905-edited. Карточка исчезла. В локальном кэше снова восемь исходных записей, DIPLOMA отсутствуют.</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>evidence/TC038-deleted.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="92" customHeight="1">
+      <x:c r="A40" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" ht="43.5">
-      <x:c r="A40" s="1" t="s">
+      <x:c r="C40" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="str">
+        <x:v>Выбрана категория День рождения. Ровно две карточки 28.10 и 21.10.2026 соответствуют исходным ID 62915 и 62917, categoryId=2.</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>evidence/TC039-birthday-category.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="92" customHeight="1">
+      <x:c r="A41" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B40" s="1" t="s">
+      <x:c r="B41" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H40" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="43.5">
-      <x:c r="A41" s="1" t="s">
+      <x:c r="C41" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="str">
+        <x:v>Период 21.10.2026 в обеих границах, GMT. Результат: одна новость День рождения, исходный ID 62917; остальные вне интервала.</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H41" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
+      <x:c r="I41" t="str">
+        <x:v>evidence/TC040-same-day.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="92" customHeight="1">
+      <x:c r="A42" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H41" s="1" t="s">
+      <x:c r="B42" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" ht="43.5">
-      <x:c r="A42" s="1" t="s">
+      <x:c r="C42" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="str">
+        <x:v>Только Активна: восемь исходных активных новостей, проверены при прокрутке. Созданная неактивная новость исключена.</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H42" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>evidence/TC041-active-top.xml
+evidence/TC041-active-middle.xml
+evidence/TC041-active-bottom.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="76" customHeight="1">
+      <x:c r="A43" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B42" s="1" t="s">
+      <x:c r="B43" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H42" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="43.5">
-      <x:c r="A43" s="1" t="s">
+      <x:c r="C43" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="str">
+        <x:v>Только Не активна: единственная созданная тестовая новость со статусом НЕ АКТИВНА; исходные активные исключены.</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H43" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>evidence/TC042-inactive-only.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="76" customHeight="1">
+      <x:c r="A44" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
+      <x:c r="B44" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H43" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="43.5">
-      <x:c r="A44" s="1" t="s">
+      <x:c r="C44" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="str">
+        <x:v>При обоих отмеченных флагах показаны активные исходные новости и созданная неактивная новость.</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H44" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>evidence/TC043-both-statuses.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="60" customHeight="1">
+      <x:c r="A45" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
+      <x:c r="B45" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D44" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H44" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="58">
-      <x:c r="A45" s="1" t="s">
+      <x:c r="C45" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
+      <x:c r="E45" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="str">
+        <x:v>На главной отображаются три новости, в общем списке шесть. Состав первых трёх совпадает.</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
+      <x:c r="H45" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
+      <x:c r="I45" t="str">
+        <x:v>evidence/TC001-main.png
+evidence/TC012-news.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="76" customHeight="1">
+      <x:c r="A46" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H45" s="1" t="s">
+      <x:c r="B46" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" ht="58">
-      <x:c r="A46" s="1" t="s">
+      <x:c r="C46" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="str">
+        <x:v>Собственная DIPLOMA-SCHEDULED на 24.10.2026 показана в панели и отсутствует в публичном списке. После проверки удалена.</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H46" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="I46" t="str">
+        <x:v>evidence/TC045-scheduled-panel.xml
+evidence/TC045-public-excluded.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="76" customHeight="1">
+      <x:c r="A47" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H46" s="1" t="s">
+      <x:c r="B47" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" ht="29">
-      <x:c r="A47" s="1" t="s">
+      <x:c r="C47" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="str">
+        <x:v>Заблокировано</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="str">
+        <x:v>Не выполнено: в задании выдана только login2 с доступом к панели. Отдельной учётной записи без прав администратора нет.</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H47" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
+      <x:c r="I47" t="str"/>
+    </x:row>
+    <x:row r="48" ht="108" customHeight="1">
+      <x:c r="A48" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H47" s="1" t="s">
+      <x:c r="B48" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" ht="43.5">
-      <x:c r="A48" s="1" t="s">
+      <x:c r="C48" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="str">
+        <x:v>Без Wi-Fi и мобильных данных вход не выполнен; показано общее сообщение Что-то пошло не так. Попробуйте позднее. После восстановления обеих сетей вход успешен.</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H48" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
+      <x:c r="I48" t="str">
+        <x:v>evidence/TC047-offline-login.png
+evidence/TC047-restored-login.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="108" customHeight="1">
+      <x:c r="A49" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H48" s="1" t="s">
+      <x:c r="B49" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-    </x:row>
-    <x:row r="49" ht="58">
-      <x:c r="A49" s="1" t="s">
+      <x:c r="C49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="str">
+        <x:v>Заблокировано</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="str">
+        <x:v>Не выполнено: второй независимый клиент и контролируемое внешнее изменение данных не подготовлены. Окончание индикатора само по себе не проверяет получение новой записи.</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H49" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
+      <x:c r="I49" t="str"/>
+    </x:row>
+    <x:row r="50" ht="108" customHeight="1">
+      <x:c r="A50" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H49" s="1" t="s">
+      <x:c r="B50" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="50" ht="58">
-      <x:c r="A50" s="1" t="s">
+      <x:c r="C50" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="str">
+        <x:v>После принудительной остановки через am force-stop и запуска открыта главная без повторного ввода реквизитов. Использован системный эквивалент кнопки Остановить.</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H50" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B50" s="1" t="s">
+      <x:c r="I50" t="str">
+        <x:v>evidence/TC049-restarted.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="140" customHeight="1">
+      <x:c r="A51" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H50" s="1" t="s">
+      <x:c r="B51" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51" ht="43.5">
-      <x:c r="A51" s="1" t="s">
+      <x:c r="C51" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="str">
+        <x:v>Не выполнено</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="str">
+        <x:v>Частично: пароль маскируется; при шрифте 1.3 просмотрены панель и создание, кнопки видимы; настройка восстановлена 1.0. Полный маршрут со шрифтом и озвучивание TalkBack не проверены. Назначение Войти в дереве указано как Сохранить.</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H51" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B51" s="1" t="s">
+      <x:c r="I51" t="str">
+        <x:v>evidence/TC050-font-panel.png
+evidence/TC050-font-create.png
+evidence/TC047-offline-login.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="108" customHeight="1">
+      <x:c r="A52" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H51" s="1" t="s">
+      <x:c r="B52" s="1" t="s">
         <x:v>142</x:v>
       </x:c>
-    </x:row>
-    <x:row r="52" ht="43.5">
-      <x:c r="A52" s="1" t="s">
+      <x:c r="C52" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="str">
+        <x:v>При повороте и возврате значения сохранены, падения нет; в альбомной ориентации кнопки доступны после прокрутки. Время 19:07. Черновик использован затем в TC058 и удалён.</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H52" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B52" s="1" t="s">
+      <x:c r="I52" t="str">
+        <x:v>evidence/TC051-before-rotation.xml
+evidence/TC051-landscape.png
+evidence/TC051-landscape-buttons.png
+evidence/TC051-returned.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="108" customHeight="1">
+      <x:c r="A53" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H52" s="1" t="s">
+      <x:c r="B53" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-    </x:row>
-    <x:row r="53" ht="43.5">
-      <x:c r="A53" s="1" t="s">
+      <x:c r="C53" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="str">
+        <x:v>Получен пустой список фильтром с обратным периодом. Показаны Здесь пока ничего нет и Обновить. После применения пустого фильтра вернулись новости; заглушка исчезла.</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H53" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B53" s="1" t="s">
+      <x:c r="I53" t="str">
+        <x:v>evidence/TC053-reverse-period.png
+evidence/TC052-restored.xml
+evidence/TC052-restored.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="108" customHeight="1">
+      <x:c r="A54" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H53" s="1" t="s">
+      <x:c r="B54" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54" ht="43.5">
-      <x:c r="A54" s="1" t="s">
+      <x:c r="C54" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="str">
+        <x:v>Требует уточнения</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="str">
+        <x:v>Период 24.10.2026-23.10.2026 принят, открыт пустой список. Ожидаемая блокировка обратного периода не подтверждена требованиями; оценка требует согласования.</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H54" s="1" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B54" s="1" t="s">
+      <x:c r="I54" t="str">
+        <x:v>evidence/TC053-reverse-period.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="92" customHeight="1">
+      <x:c r="A55" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H54" s="1" t="s">
+      <x:c r="B55" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-    </x:row>
-    <x:row r="55" ht="43.5">
-      <x:c r="A55" s="1" t="s">
+      <x:c r="C55" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="str">
+        <x:v>Заблокировано</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="str">
+        <x:v>Не выполнено: не согласована граница последней минуты суток и не подготовлены собственные записи на 23:59:00, 23:59:01, 23:59:59.</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H55" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
+      <x:c r="I55" t="str"/>
+    </x:row>
+    <x:row r="56" ht="92" customHeight="1">
+      <x:c r="A56" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="C55" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D55" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E55" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F55" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G55" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H55" s="1" t="s">
+      <x:c r="B56" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56" ht="43.5">
-      <x:c r="A56" s="1" t="s">
+      <x:c r="C56" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="str">
+        <x:v>Требует уточнения</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="str">
+        <x:v>Сняты оба флага, после применения виден список активных новостей. Значение комбинации флагов в требованиях не определено; оценка требует согласования.</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H56" s="1" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
+      <x:c r="I56" t="str">
+        <x:v>evidence/TC055-both-off.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="92" customHeight="1">
+      <x:c r="A57" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F56" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G56" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H56" s="1" t="s">
+      <x:c r="B57" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-    </x:row>
-    <x:row r="57" ht="43.5">
-      <x:c r="A57" s="1" t="s">
+      <x:c r="C57" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="str">
+        <x:v>Заблокировано</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="str">
+        <x:v>Не выполнено: максимальные длины заголовка и описания не заданы и не согласованы; нельзя подтвердить соответствие неизвестным ограничениям.</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H57" s="1" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B57" s="1" t="s">
+      <x:c r="I57" t="str"/>
+    </x:row>
+    <x:row r="58" ht="108" customHeight="1">
+      <x:c r="A58" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C57" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F57" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G57" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H57" s="1" t="s">
+      <x:c r="B58" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58" ht="58">
-      <x:c r="A58" s="1" t="s">
+      <x:c r="C58" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="str">
+        <x:v>Требует уточнения</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="str">
+        <x:v>Из формы с заголовком DIPLOMA-BACK системная Назад вернула в панель без диалога. Новость не сохранилась. Нужна спецификация подтверждения потери черновика.</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H58" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
+      <x:c r="I58" t="str">
+        <x:v>evidence/TC057-system-back.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="124" customHeight="1">
+      <x:c r="A59" s="1" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F58" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G58" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H58" s="1" t="s">
+      <x:c r="B59" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59" ht="43.5">
-      <x:c r="A59" s="1" t="s">
+      <x:c r="C59" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="str">
+        <x:v>При отключённых Wi-Fi и мобильных данных сообщение Сохранение не удалось. Попробуйте позднее; поля сохранены. После восстановления повтор создал ровно одну запись ID62964; запись удалена.</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H59" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
+      <x:c r="I59" t="str">
+        <x:v>evidence/TC058-network-error.png
+evidence/TC058-retry-created.xml
+evidence/TC058-count.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="124" customHeight="1">
+      <x:c r="A60" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F59" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G59" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H59" s="1" t="s">
+      <x:c r="B60" s="1" t="s">
         <x:v>166</x:v>
       </x:c>
-    </x:row>
-    <x:row r="60" ht="58">
-      <x:c r="A60" s="1" t="s">
+      <x:c r="C60" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="str">
+        <x:v>Доступны все восемь цитат. Раскрыты первая, вторая и последняя; пояснения читаются без наложений. После прокрутки выполнен возврат к первой.</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H60" s="1" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B60" s="1" t="s">
+      <x:c r="I60" t="str">
+        <x:v>evidence/TC010-expanded.png
+evidence/TC059-second-expanded.xml
+evidence/TC059-last-expanded.png
+evidence/TC059-return-first.xml</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="92" customHeight="1">
+      <x:c r="A61" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C60" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E60" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F60" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G60" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H60" s="1" t="s">
+      <x:c r="B61" s="1" t="s">
         <x:v>169</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61" ht="84" customHeight="1">
-      <x:c r="A61" s="1" t="s">
+      <x:c r="C61" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="str">
+        <x:v>Пройдено</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="str">
+        <x:v>Исходный APK установлен, package ru.edu.qamid, version 1.0.0 (14), targetSdk 36. На эмуляторе API 36 выполнены вход, переходы, цитаты и создание новости.</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H61" s="1" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C61" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D61" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E61" s="1" t="str">
-        <x:v>Заблокировано</x:v>
-      </x:c>
-      <x:c r="F61" s="1" t="str">
-        <x:v>Прогон не начат: ADB недоступен (Permission denied). Устройство API 36 не подключено.</x:v>
-      </x:c>
-      <x:c r="G61" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H61" s="1" t="s">
-        <x:v>172</x:v>
+      <x:c r="I61" t="str">
+        <x:v>evidence/00-launch.png
+evidence/TC001-main.png
+evidence/TC009-mission.png
+evidence/TC033-reopened.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
